--- a/MATH/M03/bus123-math-m03-l01-starter.xlsx
+++ b/MATH/M03/bus123-math-m03-l01-starter.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -133,6 +133,11 @@
       <color rgb="004A5567"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001A1F2C"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -197,7 +202,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -234,11 +239,55 @@
         <color rgb="00D9E2D9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E2D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9E2D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E2D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9E2D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -347,6 +396,20 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -745,13 +808,13 @@
           <t>Learning Objectives</t>
         </is>
       </c>
-      <c r="B4" s="31" t="n"/>
-      <c r="C4" s="31" t="n"/>
-      <c r="D4" s="31" t="n"/>
-      <c r="E4" s="31" t="n"/>
-      <c r="F4" s="31" t="n"/>
-      <c r="G4" s="31" t="n"/>
-      <c r="H4" s="31" t="n"/>
+      <c r="B4" s="42" t="n"/>
+      <c r="C4" s="42" t="n"/>
+      <c r="D4" s="42" t="n"/>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="42" t="n"/>
+      <c r="G4" s="42" t="n"/>
+      <c r="H4" s="43" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
@@ -764,12 +827,12 @@
           <t>Calculate a net price from a list price and a single trade discount.</t>
         </is>
       </c>
-      <c r="C5" s="31" t="n"/>
-      <c r="D5" s="31" t="n"/>
-      <c r="E5" s="31" t="n"/>
-      <c r="F5" s="31" t="n"/>
-      <c r="G5" s="31" t="n"/>
-      <c r="H5" s="31" t="n"/>
+      <c r="C5" s="42" t="n"/>
+      <c r="D5" s="42" t="n"/>
+      <c r="E5" s="42" t="n"/>
+      <c r="F5" s="42" t="n"/>
+      <c r="G5" s="42" t="n"/>
+      <c r="H5" s="43" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
@@ -782,12 +845,12 @@
           <t>Apply chain discounts in sequence instead of adding rates.</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="31" t="n"/>
-      <c r="E6" s="31" t="n"/>
-      <c r="F6" s="31" t="n"/>
-      <c r="G6" s="31" t="n"/>
-      <c r="H6" s="31" t="n"/>
+      <c r="C6" s="42" t="n"/>
+      <c r="D6" s="42" t="n"/>
+      <c r="E6" s="42" t="n"/>
+      <c r="F6" s="42" t="n"/>
+      <c r="G6" s="42" t="n"/>
+      <c r="H6" s="43" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
@@ -800,12 +863,12 @@
           <t>Interpret cash discount terms such as 2/10 net 30 and calculate early payment.</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="31" t="n"/>
-      <c r="F7" s="31" t="n"/>
-      <c r="G7" s="31" t="n"/>
-      <c r="H7" s="31" t="n"/>
+      <c r="C7" s="42" t="n"/>
+      <c r="D7" s="42" t="n"/>
+      <c r="E7" s="42" t="n"/>
+      <c r="F7" s="42" t="n"/>
+      <c r="G7" s="42" t="n"/>
+      <c r="H7" s="43" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
@@ -818,12 +881,12 @@
           <t>Use Excel formulas with cell references to model discount decisions.</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="31" t="n"/>
-      <c r="E8" s="31" t="n"/>
-      <c r="F8" s="31" t="n"/>
-      <c r="G8" s="31" t="n"/>
-      <c r="H8" s="31" t="n"/>
+      <c r="C8" s="42" t="n"/>
+      <c r="D8" s="42" t="n"/>
+      <c r="E8" s="42" t="n"/>
+      <c r="F8" s="42" t="n"/>
+      <c r="G8" s="42" t="n"/>
+      <c r="H8" s="43" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="30" t="inlineStr">
@@ -831,13 +894,13 @@
           <t>How to Use This Workbook</t>
         </is>
       </c>
-      <c r="B9" s="31" t="n"/>
-      <c r="C9" s="31" t="n"/>
-      <c r="D9" s="31" t="n"/>
-      <c r="E9" s="31" t="n"/>
-      <c r="F9" s="31" t="n"/>
-      <c r="G9" s="31" t="n"/>
-      <c r="H9" s="31" t="n"/>
+      <c r="B9" s="42" t="n"/>
+      <c r="C9" s="42" t="n"/>
+      <c r="D9" s="42" t="n"/>
+      <c r="E9" s="42" t="n"/>
+      <c r="F9" s="42" t="n"/>
+      <c r="G9" s="42" t="n"/>
+      <c r="H9" s="43" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
@@ -850,12 +913,12 @@
           <t>During the deck, use the Live You Try It tab for short self-graded Excel pauses.</t>
         </is>
       </c>
-      <c r="C10" s="31" t="n"/>
-      <c r="D10" s="31" t="n"/>
-      <c r="E10" s="31" t="n"/>
-      <c r="F10" s="31" t="n"/>
-      <c r="G10" s="31" t="n"/>
-      <c r="H10" s="31" t="n"/>
+      <c r="C10" s="42" t="n"/>
+      <c r="D10" s="42" t="n"/>
+      <c r="E10" s="42" t="n"/>
+      <c r="F10" s="42" t="n"/>
+      <c r="G10" s="42" t="n"/>
+      <c r="H10" s="43" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
@@ -868,12 +931,12 @@
           <t>The Live You Try It tab uses the exact numbers from slides 8, 13, and 17.</t>
         </is>
       </c>
-      <c r="C11" s="31" t="n"/>
-      <c r="D11" s="31" t="n"/>
-      <c r="E11" s="31" t="n"/>
-      <c r="F11" s="31" t="n"/>
-      <c r="G11" s="31" t="n"/>
-      <c r="H11" s="31" t="n"/>
+      <c r="C11" s="42" t="n"/>
+      <c r="D11" s="42" t="n"/>
+      <c r="E11" s="42" t="n"/>
+      <c r="F11" s="42" t="n"/>
+      <c r="G11" s="42" t="n"/>
+      <c r="H11" s="43" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
@@ -886,12 +949,12 @@
           <t>Yellow cells are yours. Type formulas whenever possible instead of hardcoding answers.</t>
         </is>
       </c>
-      <c r="C12" s="31" t="n"/>
-      <c r="D12" s="31" t="n"/>
-      <c r="E12" s="31" t="n"/>
-      <c r="F12" s="31" t="n"/>
-      <c r="G12" s="31" t="n"/>
-      <c r="H12" s="31" t="n"/>
+      <c r="C12" s="42" t="n"/>
+      <c r="D12" s="42" t="n"/>
+      <c r="E12" s="42" t="n"/>
+      <c r="F12" s="42" t="n"/>
+      <c r="G12" s="42" t="n"/>
+      <c r="H12" s="43" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
@@ -904,12 +967,12 @@
           <t>Feedback on Live You Try It is for practice and revision, not grading.</t>
         </is>
       </c>
-      <c r="C13" s="31" t="n"/>
-      <c r="D13" s="31" t="n"/>
-      <c r="E13" s="31" t="n"/>
-      <c r="F13" s="31" t="n"/>
-      <c r="G13" s="31" t="n"/>
-      <c r="H13" s="31" t="n"/>
+      <c r="C13" s="42" t="n"/>
+      <c r="D13" s="42" t="n"/>
+      <c r="E13" s="42" t="n"/>
+      <c r="F13" s="42" t="n"/>
+      <c r="G13" s="42" t="n"/>
+      <c r="H13" s="43" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="31" t="inlineStr">
@@ -922,12 +985,12 @@
           <t>The Class Challenge tab is harder and is the graded or next-level activity.</t>
         </is>
       </c>
-      <c r="C14" s="31" t="n"/>
-      <c r="D14" s="31" t="n"/>
-      <c r="E14" s="31" t="n"/>
-      <c r="F14" s="31" t="n"/>
-      <c r="G14" s="31" t="n"/>
-      <c r="H14" s="31" t="n"/>
+      <c r="C14" s="42" t="n"/>
+      <c r="D14" s="42" t="n"/>
+      <c r="E14" s="42" t="n"/>
+      <c r="F14" s="42" t="n"/>
+      <c r="G14" s="42" t="n"/>
+      <c r="H14" s="43" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="30" t="inlineStr">
@@ -935,13 +998,13 @@
           <t>Color Key</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="31" t="n"/>
-      <c r="D15" s="31" t="n"/>
-      <c r="E15" s="31" t="n"/>
-      <c r="F15" s="31" t="n"/>
-      <c r="G15" s="31" t="n"/>
-      <c r="H15" s="31" t="n"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="42" t="n"/>
+      <c r="E15" s="42" t="n"/>
+      <c r="F15" s="42" t="n"/>
+      <c r="G15" s="42" t="n"/>
+      <c r="H15" s="43" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="31" t="inlineStr">
@@ -954,12 +1017,12 @@
           <t>Your formula or answer input.</t>
         </is>
       </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="31" t="n"/>
-      <c r="E16" s="31" t="n"/>
-      <c r="F16" s="31" t="n"/>
-      <c r="G16" s="31" t="n"/>
-      <c r="H16" s="31" t="n"/>
+      <c r="C16" s="42" t="n"/>
+      <c r="D16" s="42" t="n"/>
+      <c r="E16" s="42" t="n"/>
+      <c r="F16" s="42" t="n"/>
+      <c r="G16" s="42" t="n"/>
+      <c r="H16" s="43" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
@@ -972,12 +1035,12 @@
           <t>Self-checking hints and feedback for Live You Try It.</t>
         </is>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="31" t="n"/>
-      <c r="E17" s="31" t="n"/>
-      <c r="F17" s="31" t="n"/>
-      <c r="G17" s="31" t="n"/>
-      <c r="H17" s="31" t="n"/>
+      <c r="C17" s="42" t="n"/>
+      <c r="D17" s="42" t="n"/>
+      <c r="E17" s="42" t="n"/>
+      <c r="F17" s="42" t="n"/>
+      <c r="G17" s="42" t="n"/>
+      <c r="H17" s="43" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1380,12 +1443,12 @@
         <f>COUNTIF(H5:H15,"Correct*")&amp;" of 9 complete"</f>
         <v/>
       </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="31" t="n"/>
-      <c r="E17" s="31" t="n"/>
-      <c r="F17" s="31" t="n"/>
-      <c r="G17" s="31" t="n"/>
-      <c r="H17" s="31" t="n"/>
+      <c r="C17" s="42" t="n"/>
+      <c r="D17" s="42" t="n"/>
+      <c r="E17" s="42" t="n"/>
+      <c r="F17" s="42" t="n"/>
+      <c r="G17" s="42" t="n"/>
+      <c r="H17" s="43" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1403,31 +1466,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="20" min="1" max="1"/>
     <col width="30" customWidth="1" style="20" min="2" max="2"/>
     <col width="16" customWidth="1" style="20" min="3" max="3"/>
-    <col width="16" customWidth="1" style="20" min="4" max="4"/>
+    <col width="18" customWidth="1" style="20" min="4" max="4"/>
     <col width="18" customWidth="1" style="20" min="5" max="5"/>
     <col width="18" customWidth="1" style="20" min="6" max="6"/>
     <col width="18" customWidth="1" style="20" min="7" max="7"/>
     <col width="18" customWidth="1" style="20" min="8" max="8"/>
-    <col width="34" customWidth="1" style="20" min="9" max="9"/>
+    <col width="36" customWidth="1" style="20" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="20">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>M03 · L01 — Class Challenge</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="38" customHeight="1" s="20">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Graded or next-level activity: combine trade or chain discounts with cash discount terms.</t>
+    <row r="2" ht="42" customHeight="1" s="20">
+      <c r="A2" s="41" t="inlineStr">
+        <is>
+          <t>Robust graded or next-level activity: combine trade or chain discounts with cash discount terms across ten Tidal Goods scenarios.</t>
         </is>
       </c>
     </row>
@@ -1479,30 +1542,30 @@
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" s="20">
-      <c r="A5" s="31" t="n">
+      <c r="A5" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Wetsuit Order (50 units)</t>
         </is>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="45" t="n">
         <v>9499.5</v>
       </c>
-      <c r="D5" s="31" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="E5" s="31" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>2/10 net 30</t>
         </is>
       </c>
-      <c r="F5" s="38" t="inlineStr"/>
-      <c r="G5" s="38" t="inlineStr"/>
-      <c r="H5" s="38" t="inlineStr"/>
+      <c r="F5" s="46" t="inlineStr"/>
+      <c r="G5" s="46" t="inlineStr"/>
+      <c r="H5" s="46" t="inlineStr"/>
       <c r="I5" s="36" t="inlineStr">
         <is>
           <t>Use the slide 8 trade-discount logic, then the cash discount.</t>
@@ -1510,30 +1573,30 @@
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" s="20">
-      <c r="A6" s="31" t="n">
+      <c r="A6" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>Board Accessories</t>
         </is>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="45" t="n">
         <v>3625</v>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="44" t="inlineStr">
         <is>
           <t>20/10</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="44" t="inlineStr">
         <is>
           <t>1.5/10 net 30</t>
         </is>
       </c>
-      <c r="F6" s="38" t="inlineStr"/>
-      <c r="G6" s="38" t="inlineStr"/>
-      <c r="H6" s="38" t="inlineStr"/>
+      <c r="F6" s="46" t="inlineStr"/>
+      <c r="G6" s="46" t="inlineStr"/>
+      <c r="H6" s="46" t="inlineStr"/>
       <c r="I6" s="36" t="inlineStr">
         <is>
           <t>Apply the chain discount before the cash discount.</t>
@@ -1541,82 +1604,277 @@
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" s="20">
-      <c r="A7" s="31" t="n">
+      <c r="A7" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>Seasonal Display Racks</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="45" t="n">
         <v>2800</v>
       </c>
-      <c r="D7" s="31" t="inlineStr">
+      <c r="D7" s="44" t="inlineStr">
         <is>
           <t>15/5</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="44" t="inlineStr">
         <is>
           <t>3/15 net 45</t>
         </is>
       </c>
-      <c r="F7" s="38" t="inlineStr"/>
-      <c r="G7" s="38" t="inlineStr"/>
-      <c r="H7" s="38" t="inlineStr"/>
+      <c r="F7" s="46" t="inlineStr"/>
+      <c r="G7" s="46" t="inlineStr"/>
+      <c r="H7" s="46" t="inlineStr"/>
       <c r="I7" s="36" t="inlineStr">
         <is>
           <t>Use both complements, then the early-payment terms.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="31" t="n"/>
-      <c r="B8" s="31" t="n"/>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="31" t="n"/>
-      <c r="E8" s="31" t="n"/>
-      <c r="F8" s="31" t="n"/>
-      <c r="G8" s="31" t="n"/>
-      <c r="H8" s="31" t="n"/>
-      <c r="I8" s="31" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="n"/>
-      <c r="B9" s="31" t="n"/>
-      <c r="C9" s="31" t="n"/>
-      <c r="D9" s="31" t="n"/>
-      <c r="E9" s="31" t="n"/>
-      <c r="F9" s="31" t="n"/>
-      <c r="G9" s="31" t="n"/>
-      <c r="H9" s="31" t="n"/>
-      <c r="I9" s="31" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="n"/>
-      <c r="B10" s="31" t="inlineStr">
+    <row r="8" ht="42" customHeight="1" s="20">
+      <c r="A8" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>Paddle Board Demo Fleet</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="n">
+        <v>4475</v>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>15/10/5</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="inlineStr">
+        <is>
+          <t>2/10 net 30</t>
+        </is>
+      </c>
+      <c r="F8" s="46" t="inlineStr"/>
+      <c r="G8" s="46" t="inlineStr"/>
+      <c r="H8" s="46" t="inlineStr"/>
+      <c r="I8" s="36" t="inlineStr">
+        <is>
+          <t>Three trade discounts, then the early-payment discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" s="20">
+      <c r="A9" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="44" t="inlineStr">
+        <is>
+          <t>Roof Rack Bundle</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="n">
+        <v>2180</v>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>1/10 net 30</t>
+        </is>
+      </c>
+      <c r="F9" s="46" t="inlineStr"/>
+      <c r="G9" s="46" t="inlineStr"/>
+      <c r="H9" s="46" t="inlineStr"/>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>Single trade discount with a smaller cash discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" s="20">
+      <c r="A10" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="44" t="inlineStr">
+        <is>
+          <t>Dry Bag Restock</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="n">
+        <v>4350</v>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>20/15/10</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>2.5/10 net 45</t>
+        </is>
+      </c>
+      <c r="F10" s="46" t="inlineStr"/>
+      <c r="G10" s="46" t="inlineStr"/>
+      <c r="H10" s="46" t="inlineStr"/>
+      <c r="I10" s="36" t="inlineStr">
+        <is>
+          <t>Watch the third chain discount and the 2.5% cash term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" s="20">
+      <c r="A11" s="44" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>Rash Guard Bulk Buy</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="n">
+        <v>3596</v>
+      </c>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>25/5</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="inlineStr">
+        <is>
+          <t>2/15 net 45</t>
+        </is>
+      </c>
+      <c r="F11" s="46" t="inlineStr"/>
+      <c r="G11" s="46" t="inlineStr"/>
+      <c r="H11" s="46" t="inlineStr"/>
+      <c r="I11" s="36" t="inlineStr">
+        <is>
+          <t>Two-step chain discount; cash discount has a longer window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1" s="20">
+      <c r="A12" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>Fin Set Reorder</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t>20/10/5</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>1.5/10 net 30</t>
+        </is>
+      </c>
+      <c r="F12" s="46" t="inlineStr"/>
+      <c r="G12" s="46" t="inlineStr"/>
+      <c r="H12" s="46" t="inlineStr"/>
+      <c r="I12" s="36" t="inlineStr">
+        <is>
+          <t>Reuses the slide 13 chain structure at a larger order size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" s="20">
+      <c r="A13" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>Window Display Refresh</t>
+        </is>
+      </c>
+      <c r="C13" s="45" t="n">
+        <v>6750</v>
+      </c>
+      <c r="D13" s="44" t="inlineStr">
+        <is>
+          <t>18/7</t>
+        </is>
+      </c>
+      <c r="E13" s="44" t="inlineStr">
+        <is>
+          <t>3/15 net 45</t>
+        </is>
+      </c>
+      <c r="F13" s="46" t="inlineStr"/>
+      <c r="G13" s="46" t="inlineStr"/>
+      <c r="H13" s="46" t="inlineStr"/>
+      <c r="I13" s="36" t="inlineStr">
+        <is>
+          <t>Intermediate chain rates plus a stronger cash discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1" s="20">
+      <c r="A14" s="44" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="44" t="inlineStr">
+        <is>
+          <t>Accessory Launch Pack</t>
+        </is>
+      </c>
+      <c r="C14" s="45" t="n">
+        <v>5125</v>
+      </c>
+      <c r="D14" s="44" t="inlineStr">
+        <is>
+          <t>12/8/5</t>
+        </is>
+      </c>
+      <c r="E14" s="44" t="inlineStr">
+        <is>
+          <t>2/10 net 30</t>
+        </is>
+      </c>
+      <c r="F14" s="46" t="inlineStr"/>
+      <c r="G14" s="46" t="inlineStr"/>
+      <c r="H14" s="46" t="inlineStr"/>
+      <c r="I14" s="36" t="inlineStr">
+        <is>
+          <t>Full mixed case: three chain rates and cash terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="44" t="n"/>
+      <c r="B16" s="47" t="inlineStr">
         <is>
           <t>Submission reminder</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Complete the yellow cells in F:H. Live You Try It is practice; this tab is the challenge.</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="n"/>
-      <c r="E10" s="31" t="n"/>
-      <c r="F10" s="31" t="n"/>
-      <c r="G10" s="31" t="n"/>
-      <c r="H10" s="31" t="n"/>
-      <c r="I10" s="31" t="n"/>
+      <c r="C16" s="47" t="inlineStr">
+        <is>
+          <t>Complete all yellow cells in F:H. Live You Try It is practice; this tab is the robust challenge.</t>
+        </is>
+      </c>
+      <c r="D16" s="47" t="n"/>
+      <c r="E16" s="47" t="n"/>
+      <c r="F16" s="47" t="n"/>
+      <c r="G16" s="47" t="n"/>
+      <c r="H16" s="47" t="n"/>
+      <c r="I16" s="47" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="C10:I10"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="C16:I16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MATH/M03/bus123-math-m03-l01-starter.xlsx
+++ b/MATH/M03/bus123-math-m03-l01-starter.xlsx
@@ -2,9 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="580" windowWidth="25600" windowHeight="15300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" state="visible" r:id="rId2"/>
@@ -12,7 +9,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
@@ -23,123 +19,127 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FF0E1116"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FF4A7C5E"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <color rgb="FF0A3D6B"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <color rgb="FF1A6B3C"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <i val="1"/>
       <color rgb="FF7A8290"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FFB8843D"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Consolas"/>
-      <family val="2"/>
       <color rgb="FF0E1116"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <color rgb="FF4A5567"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Aptos Display"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Aptos"/>
       <i val="1"/>
-      <color rgb="00355773"/>
+      <color rgb="FF355773"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="001A1F2C"/>
+      <color rgb="FF1A1F2C"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
       <i val="1"/>
-      <color rgb="004A5567"/>
+      <color rgb="FF4A5567"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
-      <color rgb="001A1F2C"/>
+      <color rgb="FF1A1F2C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFB8843D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF1A1F2C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF355773"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -173,43 +173,77 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E1116"/>
+        <fgColor rgb="FF0E1116"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF3EC"/>
+        <fgColor rgb="FFEAF3EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2EEE5"/>
+        <fgColor rgb="FFF2EEE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00355773"/>
+        <fgColor rgb="FF355773"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E1116"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2EEE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E1116"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2EEE5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="8">
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FFE2E8F0"/>
@@ -223,71 +257,72 @@
       <bottom style="thin">
         <color rgb="FFE2E8F0"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9E2D9"/>
+        <color rgb="FFD9E2D9"/>
       </left>
       <right style="thin">
-        <color rgb="00D9E2D9"/>
+        <color rgb="FFD9E2D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D9E2D9"/>
+        <color rgb="FFD9E2D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9E2D9"/>
+        <color rgb="FFD9E2D9"/>
       </bottom>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
-        <color rgb="00D9E2D9"/>
+        <color rgb="FFD9E2D9"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="thin">
-        <color rgb="00D9E2D9"/>
+        <color rgb="FFD9E2D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D9E2D9"/>
+        <color rgb="FFD9E2D9"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
-        <color rgb="00D9E2D9"/>
+        <color rgb="FFD9E2D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9E2D9"/>
+        <color rgb="FFD9E2D9"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="thin">
-        <color rgb="00D9E2D9"/>
+        <color rgb="FFD9E2D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D9E2D9"/>
+        <color rgb="FFD9E2D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9E2D9"/>
+        <color rgb="FFD9E2D9"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E1D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E1D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E1D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E1D6"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -410,11 +445,51 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -487,7 +562,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -529,72 +604,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -650,7 +667,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -659,13 +676,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -699,17 +716,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -764,8 +770,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1061,7 +1065,7 @@
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="B5:H5"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1456,7 +1460,7 @@
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1863,12 +1867,12 @@
           <t>Complete all yellow cells in F:H. Live You Try It is practice; this tab is the robust challenge.</t>
         </is>
       </c>
-      <c r="D16" s="47" t="n"/>
-      <c r="E16" s="47" t="n"/>
-      <c r="F16" s="47" t="n"/>
-      <c r="G16" s="47" t="n"/>
-      <c r="H16" s="47" t="n"/>
-      <c r="I16" s="47" t="n"/>
+      <c r="D16" s="42" t="n"/>
+      <c r="E16" s="42" t="n"/>
+      <c r="F16" s="42" t="n"/>
+      <c r="G16" s="42" t="n"/>
+      <c r="H16" s="42" t="n"/>
+      <c r="I16" s="43" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1876,7 +1880,7 @@
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C16:I16"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1889,207 +1893,171 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" style="20" min="1" max="1"/>
-    <col width="42" customWidth="1" style="20" min="2" max="2"/>
-    <col width="42" customWidth="1" style="20" min="3" max="3"/>
-    <col width="34" customWidth="1" style="20" min="4" max="4"/>
+    <col width="21.11000061035156" customWidth="1" style="20" min="1" max="1"/>
+    <col width="25.55999946594238" customWidth="1" style="20" min="2" max="2"/>
+    <col width="34.43999862670898" customWidth="1" style="20" min="3" max="3"/>
+    <col width="33.33000183105469" customWidth="1" style="20" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="40" t="inlineStr">
-        <is>
-          <t>Formula Reference Card — Discounts</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="41" t="inlineStr">
-        <is>
-          <t>Use this as a syntax reminder, then return to the yellow cells.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+    <row r="1" ht="31.5" customHeight="1" s="20">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
-        <is>
-          <t>Excel Syntax</t>
-        </is>
-      </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>Manual Math</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="B1" s="61" t="inlineStr">
+        <is>
+          <t>Excel Pattern</t>
+        </is>
+      </c>
+      <c r="C1" s="61" t="inlineStr">
+        <is>
+          <t>Plain-English Meaning</t>
+        </is>
+      </c>
+      <c r="D1" s="61" t="inlineStr">
         <is>
           <t>Watch Out For</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+    <row r="2" ht="31.5" customHeight="1" s="20">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Trade complement</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>'=1 - discount_rate</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>1 - 0.30 = 0.70</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
+      <c r="B2" s="67" t="inlineStr">
+        <is>
+          <t>=1-discount_rate</t>
+        </is>
+      </c>
+      <c r="C2" s="65" t="inlineStr">
+        <is>
+          <t>Finds the percent the buyer still pays.</t>
+        </is>
+      </c>
+      <c r="D2" s="68" t="inlineStr">
         <is>
           <t>Use the complement for net price.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+    <row r="3" ht="31.5" customHeight="1" s="20">
+      <c r="A3" s="65" t="inlineStr">
         <is>
           <t>Trade discount amount</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
-        <is>
-          <t>'=list_price * discount_rate</t>
-        </is>
-      </c>
-      <c r="C6" s="31" t="inlineStr">
-        <is>
-          <t>$189.99 * 0.30 = $57.00</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr">
-        <is>
-          <t>This is savings, not payment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="B3" s="67" t="inlineStr">
+        <is>
+          <t>=list_price*discount_rate</t>
+        </is>
+      </c>
+      <c r="C3" s="65" t="inlineStr">
+        <is>
+          <t>Calculates the savings from the listed price.</t>
+        </is>
+      </c>
+      <c r="D3" s="68" t="inlineStr">
+        <is>
+          <t>This is savings, not the payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" s="20">
+      <c r="A4" s="65" t="inlineStr">
         <is>
           <t>Trade net price</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>'=list_price * (1 - discount_rate)</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>$189.99 * 0.70 = $132.99</t>
-        </is>
-      </c>
-      <c r="D7" s="31" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
+        <is>
+          <t>=list_price*(1-discount_rate)</t>
+        </is>
+      </c>
+      <c r="C4" s="65" t="inlineStr">
+        <is>
+          <t>Calculates the buyer price after the discount.</t>
+        </is>
+      </c>
+      <c r="D4" s="68" t="inlineStr">
         <is>
           <t>Net price is what the buyer pays.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+    <row r="5" ht="31.5" customHeight="1" s="20">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>Chain net price</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>'=list_price*(1-d1)*(1-d2)*(1-d3)</t>
-        </is>
-      </c>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>$64 * 0.80 * 0.90 * 0.95 = $43.78</t>
-        </is>
-      </c>
-      <c r="D8" s="31" t="inlineStr">
-        <is>
-          <t>Do not add the rates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="B5" s="67" t="inlineStr">
+        <is>
+          <t>=list_price*(1-d1)*(1-d2)*(1-d3)</t>
+        </is>
+      </c>
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>Applies each discount one at a time.</t>
+        </is>
+      </c>
+      <c r="D5" s="68" t="inlineStr">
+        <is>
+          <t>Do not add chained discount rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" s="20">
+      <c r="A6" s="65" t="inlineStr">
         <is>
           <t>Single equivalent discount</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>'=1-((1-d1)*(1-d2)*(1-d3))</t>
-        </is>
-      </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>1 - 0.684 = 31.6%</t>
-        </is>
-      </c>
-      <c r="D9" s="31" t="inlineStr">
-        <is>
-          <t>Format as a percent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>Cash discount amount</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>'=invoice * cash_discount_rate</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>$4,200 * 0.02 = $84</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>This is the savings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="B6" s="67" t="inlineStr">
+        <is>
+          <t>=1-((1-d1)*(1-d2)*(1-d3))</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="inlineStr">
+        <is>
+          <t>Converts a chain into one comparable discount.</t>
+        </is>
+      </c>
+      <c r="D6" s="68" t="inlineStr">
+        <is>
+          <t>Format the result as a percent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="31.5" customHeight="1" s="20">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>Early payment</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>'=invoice * (1 - cash_discount_rate)</t>
-        </is>
-      </c>
-      <c r="C11" s="31" t="inlineStr">
-        <is>
-          <t>$4,200 * 0.98 = $4,116</t>
-        </is>
-      </c>
-      <c r="D11" s="31" t="inlineStr">
-        <is>
-          <t>This is the payment amount.</t>
-        </is>
-      </c>
-    </row>
+      <c r="B7" s="67" t="inlineStr">
+        <is>
+          <t>=invoice*(1-cash_discount_rate)</t>
+        </is>
+      </c>
+      <c r="C7" s="65" t="inlineStr">
+        <is>
+          <t>Calculates the invoice after a cash discount.</t>
+        </is>
+      </c>
+      <c r="D7" s="68" t="inlineStr">
+        <is>
+          <t>Use only when payment is inside the discount window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MATH/M03/bus123-math-m03-l01-starter.xlsx
+++ b/MATH/M03/bus123-math-m03-l01-starter.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R6b29f3fe367c4cc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rd948623b171b4ddd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R3825c133218b4157"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R68e76b64d1074ff0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Quotes" sheetId="5" r:id="Rb5b98503b18e435c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R304e686a0d7e46f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R0fa4bf6bf1f846c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Rd76f9f7bf09840fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R9b286bfbf4ea4b63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Quotes" sheetId="5" r:id="Ra4ebb27f6f25461e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,13 +17,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <x:numFmt numFmtId="165" formatCode="0.0%"/>
     <x:numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <x:numFmt numFmtId="200" formatCode="0"/>
+    <x:numFmt numFmtId="201" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="27">
+  <x:fonts count="29">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -178,8 +179,19 @@
       <x:color rgb="FF9C4A2B"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1A1F2C"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF355773"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="29">
+  <x:fills count="32">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -319,6 +331,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF355773"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF355773"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -416,7 +443,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="126">
+  <x:cellXfs count="147">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -705,10 +732,97 @@
     <x:xf numFmtId="0" fontId="19" fillId="24" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="29" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="29" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="31" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="31" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="2">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF4A7C5E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFEAF3EC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C4A2B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF2EEE5"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
   <x:colors>
     <x:indexedColors>
       <x:rgbColor rgb="00000000"/>
@@ -1213,7 +1327,7 @@
         <x:v>Green feedback</x:v>
       </x:c>
       <x:c r="B18" s="89" t="str">
-        <x:v>Self-checking hints and feedback on Live You Try It.</x:v>
+        <x:v>One diagnostic feedback column confirms or redirects after you enter a formula.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1229,14 +1343,14 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10" style="20" customWidth="1"/>
-    <x:col min="2" max="2" width="34" style="20" customWidth="1"/>
-    <x:col min="3" max="3" width="14" style="20" customWidth="1"/>
-    <x:col min="4" max="4" width="14" style="20" customWidth="1"/>
-    <x:col min="5" max="5" width="16" style="20" customWidth="1"/>
-    <x:col min="6" max="6" width="20" style="20" customWidth="1"/>
-    <x:col min="7" max="7" width="32" style="20" customWidth="1"/>
-    <x:col min="8" max="8" width="36" style="20" customWidth="1"/>
+    <x:col min="1" max="1" width="10" style="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" style="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" style="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" style="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" style="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="21" style="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="45" style="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" style="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="20" customFormat="1" ht="30" customHeight="1">
@@ -1247,166 +1361,119 @@
       </x:c>
     </x:row>
     <x:row r="2" s="20" customFormat="1" ht="38" customHeight="1">
-      <x:c r="A2" s="29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Self-graded Excel pauses using the exact numbers from slides 8, 13, and 17.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Slide</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Scenario</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input A</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input B</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input C</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Your Formula / Answer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Formula Hint</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H4" s="32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Feedback</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5" s="20" customFormat="1" ht="36" customHeight="1">
+      <x:c r="A2" s="29" t="str">
+        <x:v>Self-graded Excel pauses using fresh numbers from slides 8, 13, and 17. Enter formulas first; then read Feedback.</x:v>
+      </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+    </x:row>
+    <x:row r="4" ht="26" customHeight="1">
+      <x:c r="A4" s="32" t="str">
+        <x:v>Slide</x:v>
+      </x:c>
+      <x:c r="B4" s="32" t="str">
+        <x:v>Scenario</x:v>
+      </x:c>
+      <x:c r="C4" s="32" t="str">
+        <x:v>Input A</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="str">
+        <x:v>Input B</x:v>
+      </x:c>
+      <x:c r="E4" s="32" t="str">
+        <x:v>Input C</x:v>
+      </x:c>
+      <x:c r="F4" s="32" t="str">
+        <x:v>Your Formula / Answer</x:v>
+      </x:c>
+      <x:c r="G4" s="135" t="str">
+        <x:v>Feedback</x:v>
+      </x:c>
+      <x:c r="H4" s="135" t="str">
+        <x:v>Business Meaning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A5" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B5" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trade complement for wetsuit</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>189.99</x:v>
-      </x:c>
-      <x:c r="D5" s="34" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E5" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="35" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">'=1 - discount rate</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="37" t="str">
-        <x:f>IF(F5="","Hint: "&amp;G5,IF(ROUND(F5,4)=ROUND(1-D5,4),"Correct - self-check complete","Try again - use 1 minus the discount rate"))</x:f>
-        <x:v>Hint: '=1 - discount rate</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" s="20" customFormat="1" ht="36" customHeight="1">
+      <x:c r="B5" s="145" t="str">
+        <x:v>Trade complement for travel duffel</x:v>
+      </x:c>
+      <x:c r="C5" s="126" t="n">
+        <x:v>148.5</x:v>
+      </x:c>
+      <x:c r="D5" s="127" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="E5" s="145"/>
+      <x:c r="F5" s="128"/>
+      <x:c r="G5" s="140" t="str">
+        <x:f>IF(F5="","Enter a formula, then check.",IF(ROUND(F5,4)=ROUND(1-D5,4),"Correct - complement is 76%.","Try again - what percent remains after the discount?"))</x:f>
+        <x:v>Enter a formula, then check.</x:v>
+      </x:c>
+      <x:c r="H5" s="144" t="str">
+        <x:v>Percent of list price the buyer pays</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A6" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trade discount amount</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>189.99</x:v>
-      </x:c>
-      <x:c r="D6" s="34" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E6" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="38" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">'=list price * discount rate</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H6" s="37" t="str">
-        <x:f>IF(F6="","Hint: "&amp;G6,IF(ROUND(F6,2)=ROUND(C6*D6,2),"Correct - self-check complete","Try again - this finds the dollars saved"))</x:f>
-        <x:v>Hint: '=list price * discount rate</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" s="20" customFormat="1" ht="36" customHeight="1">
+      <x:c r="B6" s="145" t="str">
+        <x:v>Trade discount amount</x:v>
+      </x:c>
+      <x:c r="C6" s="126" t="n">
+        <x:v>148.5</x:v>
+      </x:c>
+      <x:c r="D6" s="127" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="E6" s="145"/>
+      <x:c r="F6" s="129"/>
+      <x:c r="G6" s="140" t="str">
+        <x:f>IF(F6="","Enter a formula, then check.",IF(ROUND(F6,2)=ROUND(C6*D6,2),"Correct - discount amount is $35.64.","Try again - this row asks for dollars saved, not the payment."))</x:f>
+        <x:v>Enter a formula, then check.</x:v>
+      </x:c>
+      <x:c r="H6" s="144" t="str">
+        <x:v>Dollars removed from list price</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A7" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B7" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trade net price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>189.99</x:v>
-      </x:c>
-      <x:c r="D7" s="34" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F7" s="38" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G7" s="36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">'=list price * complement</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H7" s="37" t="str">
-        <x:f>IF(F7="","Hint: "&amp;G7,IF(ROUND(F7,2)=ROUND(C7*(1-D7),2),"Correct - self-check complete","Try again - net price is what Tidal Goods pays"))</x:f>
-        <x:v>Hint: '=list price * complement</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" s="20" customFormat="1" ht="36" customHeight="1">
+      <x:c r="B7" s="145" t="str">
+        <x:v>Trade net price</x:v>
+      </x:c>
+      <x:c r="C7" s="126" t="n">
+        <x:v>148.5</x:v>
+      </x:c>
+      <x:c r="D7" s="127" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="E7" s="145"/>
+      <x:c r="F7" s="129"/>
+      <x:c r="G7" s="140" t="str">
+        <x:f>IF(F7="","Enter a formula, then check.",IF(ROUND(F7,2)=ROUND(C7*(1-D7),2),"Correct - net price is $112.86.","Try again - multiply the list price by the complement."))</x:f>
+        <x:v>Enter a formula, then check.</x:v>
+      </x:c>
+      <x:c r="H7" s="144" t="str">
+        <x:v>Amount Tidal Goods pays</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A8" s="39" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="B8" s="39" t="inlineStr">
+      <x:c r="B8" s="146" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
@@ -1421,143 +1488,93 @@
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E8" s="39" t="inlineStr">
+      <x:c r="E8" s="146" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="F8" s="39" t="inlineStr">
+      <x:c r="F8" s="39"/>
+      <x:c r="G8" s="141" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="G8" s="39" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H8" s="39" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="9" s="20" customFormat="1" ht="36" customHeight="1">
+      <x:c r="H8" s="144"/>
+    </x:row>
+    <x:row r="9" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A9" s="31" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chain net price for surfboard fins</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D9" s="34" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="E9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10% / 5%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="38" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G9" s="36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">'=list price*(1-d1)*(1-d2)*(1-d3)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9" s="37" t="str">
-        <x:f>IF(F9="","Hint: "&amp;G9,IF(ROUND(F9,2)=ROUND(C9*(1-D9)*(1-0.10)*(1-0.05),2),"Correct - self-check complete","Try again - multiply each complement in order"))</x:f>
-        <x:v>Hint: '=list price*(1-d1)*(1-d2)*(1-d3)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" s="20" customFormat="1" ht="36" customHeight="1">
+      <x:c r="B9" s="145" t="str">
+        <x:v>Chain net price (d3 is in Input A below)</x:v>
+      </x:c>
+      <x:c r="C9" s="126" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D9" s="127" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E9" s="127" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="F9" s="129"/>
+      <x:c r="G9" s="140" t="str">
+        <x:f>IF(F9="","Enter a formula, then check.",IF(ROUND(F9,2)=ROUND(C9*(1-D9)*(1-E9)*(1-C10),2),"Correct - chain net price is $150.48.","Try again - use all three complements in sequence."))</x:f>
+        <x:v>Enter a formula, then check.</x:v>
+      </x:c>
+      <x:c r="H9" s="144" t="str">
+        <x:v>Final price after all three discounts</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A10" s="31" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Single equivalent discount rate</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="31" t="n">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">20% / 10% / 5%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="35" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G10" s="36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">'=1 - combined complement</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H10" s="37" t="str">
-        <x:f>IF(F10="","Hint: "&amp;G10,IF(ROUND(F10,4)=ROUND(1-((1-0.20)*(1-0.10)*(1-0.05)),4),"Correct - self-check complete","Try again - subtract the combined complement from 1"))</x:f>
-        <x:v>Hint: '=1 - combined complement</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" s="20" customFormat="1" ht="36" customHeight="1">
+      <x:c r="B10" s="145" t="str">
+        <x:v>Single equivalent rate; d3</x:v>
+      </x:c>
+      <x:c r="C10" s="130" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="D10" s="31"/>
+      <x:c r="E10" s="145"/>
+      <x:c r="F10" s="131"/>
+      <x:c r="G10" s="140" t="str">
+        <x:f>IF(F10="","Enter a formula, then check.",IF(ROUND(F10,4)=ROUND(1-((1-D9)*(1-E9)*(1-C10)),4),"Correct - equivalent discount is 37.3%.","Try again - subtract the combined complement from 1."))</x:f>
+        <x:v>Enter a formula, then check.</x:v>
+      </x:c>
+      <x:c r="H10" s="144" t="str">
+        <x:v>One rate with the same pricing effect</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A11" s="31" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Difference from adding rates shortcut</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="31" t="n">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">35% shortcut</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="38" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G11" s="36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">'=chain price - shortcut price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H11" s="37" t="str">
-        <x:f>IF(F11="","Hint: "&amp;G11,IF(ROUND(F11,2)=ROUND((64*(1-0.20)*(1-0.10)*(1-0.05))-(64*(1-0.35)),2),"Correct - self-check complete","Try again - compare $43.78 to $41.60"))</x:f>
-        <x:v>Hint: '=chain price - shortcut price</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" s="20" customFormat="1" ht="36" customHeight="1">
+      <x:c r="B11" s="145" t="str">
+        <x:v>Difference from 42% adding-rates shortcut</x:v>
+      </x:c>
+      <x:c r="C11" s="130" t="n">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="D11" s="31"/>
+      <x:c r="E11" s="145"/>
+      <x:c r="F11" s="129"/>
+      <x:c r="G11" s="140" t="str">
+        <x:f>IF(F11="","Enter a formula, then check.",IF(ROUND(F11,2)=ROUND((C9*(1-D9)*(1-E9)*(1-C10))-(C9*(1-C11)),2),"Correct - shortcut difference is $11.28.","Try again - compare the chain price with the 42% shortcut price."))</x:f>
+        <x:v>Enter a formula, then check.</x:v>
+      </x:c>
+      <x:c r="H11" s="144" t="str">
+        <x:v>Cost of using the invalid shortcut</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A12" s="39" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="B12" s="39" t="inlineStr">
+      <x:c r="B12" s="146" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
@@ -1572,130 +1589,92 @@
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E12" s="39" t="inlineStr">
+      <x:c r="E12" s="146" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="F12" s="39" t="inlineStr">
+      <x:c r="F12" s="39"/>
+      <x:c r="G12" s="141" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="G12" s="39" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="39" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="13" s="20" customFormat="1" ht="36" customHeight="1">
+      <x:c r="H12" s="144"/>
+    </x:row>
+    <x:row r="13" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A13" s="31" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cash discount amount</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>4200</x:v>
-      </x:c>
-      <x:c r="D13" s="34" t="n">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="E13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2/10 net 30</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="38" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G13" s="36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">'=invoice * discount rate</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" s="37" t="str">
-        <x:f>IF(F13="","Hint: "&amp;G13,IF(ROUND(F13,2)=ROUND(C13*D13,2),"Correct - self-check complete","Try again - this finds the savings"))</x:f>
-        <x:v>Hint: '=invoice * discount rate</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" s="20" customFormat="1" ht="36" customHeight="1">
+      <x:c r="B13" s="145" t="str">
+        <x:v>Cash discount amount</x:v>
+      </x:c>
+      <x:c r="C13" s="126" t="n">
+        <x:v>3750</x:v>
+      </x:c>
+      <x:c r="D13" s="127" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="E13" s="145" t="str">
+        <x:v>3/15 net 45</x:v>
+      </x:c>
+      <x:c r="F13" s="129"/>
+      <x:c r="G13" s="140" t="str">
+        <x:f>IF(F13="","Enter a formula, then check.",IF(ROUND(F13,2)=ROUND(C13*D13,2),"Correct - discount amount is $112.50.","Try again - this row asks for the dollars saved."))</x:f>
+        <x:v>Enter a formula, then check.</x:v>
+      </x:c>
+      <x:c r="H13" s="144" t="str">
+        <x:v>Dollars saved for paying early</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A14" s="31" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B14" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Early payment amount</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>4200</x:v>
-      </x:c>
-      <x:c r="D14" s="34" t="n">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="E14" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2/10 net 30</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" s="38" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G14" s="36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">'=invoice * (1 - discount rate)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H14" s="37" t="str">
-        <x:f>IF(F14="","Hint: "&amp;G14,IF(ROUND(F14,2)=ROUND(C14*(1-D14),2),"Correct - self-check complete","Try again - subtract the discount from the invoice"))</x:f>
-        <x:v>Hint: '=invoice * (1 - discount rate)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" s="20" customFormat="1" ht="36" customHeight="1">
+      <x:c r="B14" s="145" t="str">
+        <x:v>Early payment amount</x:v>
+      </x:c>
+      <x:c r="C14" s="126" t="n">
+        <x:v>3750</x:v>
+      </x:c>
+      <x:c r="D14" s="127" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="E14" s="145" t="str">
+        <x:v>3/15 net 45</x:v>
+      </x:c>
+      <x:c r="F14" s="129"/>
+      <x:c r="G14" s="140" t="str">
+        <x:f>IF(F14="","Enter a formula, then check.",IF(ROUND(F14,2)=ROUND(C14*(1-D14),2),"Correct - early payment is $3,637.50.","Try again - multiply the invoice by the complement."))</x:f>
+        <x:v>Enter a formula, then check.</x:v>
+      </x:c>
+      <x:c r="H14" s="144" t="str">
+        <x:v>Amount sent to the supplier</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" s="20" customFormat="1" ht="42" customHeight="1">
       <x:c r="A15" s="31" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B15" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savings from paying early</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>4200</x:v>
-      </x:c>
-      <x:c r="D15" s="34" t="n">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="E15" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2/10 net 30</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" s="38" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G15" s="36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">'=invoice - early payment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" s="37" t="str">
-        <x:f>IF(F15="","Hint: "&amp;G15,IF(ROUND(F15,2)=ROUND(C15-(C15*(1-D15)),2),"Correct - self-check complete","Try again - savings equals the discount amount"))</x:f>
-        <x:v>Hint: '=invoice - early payment</x:v>
+      <x:c r="B15" s="145" t="str">
+        <x:v>Cash discount eligible? 1 = Yes; 0 = No</x:v>
+      </x:c>
+      <x:c r="C15" s="132" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D15" s="132" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="145" t="str">
+        <x:v>planned day / deadline</x:v>
+      </x:c>
+      <x:c r="F15" s="133"/>
+      <x:c r="G15" s="140" t="str">
+        <x:f>IF(F15="","Enter a formula, then check.",IF(F15=IF(C15&lt;=D15,1,0),"Correct - day 12 qualifies, so eligibility is 1.","Try again - compare planned payment day 12 with deadline day 15."))</x:f>
+        <x:v>Enter a formula, then check.</x:v>
+      </x:c>
+      <x:c r="H15" s="144" t="str">
+        <x:v>Timing test completed before payment</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1715,7 +1694,7 @@
         </x:is>
       </x:c>
       <x:c r="B17" s="31" t="str">
-        <x:f>COUNTIF(H5:H15,"Correct - self-check complete")&amp;" of 9 complete"</x:f>
+        <x:f>COUNTIF(G5:G15,"Correct*")&amp;" of 9 complete"</x:f>
         <x:v>0 of 9 complete</x:v>
       </x:c>
       <x:c r="C17" s="42" t="n"/>
@@ -1731,6 +1710,10 @@
     <x:mergeCell ref="B17:H17"/>
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="G5:G15">
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Correct"/>
+    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Try again"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
